--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_406_R47.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_406_R47.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.209199999999999</v>
+        <v>7.7244</v>
       </c>
       <c r="E2" t="n">
         <v>6.3604</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8488</v>
+        <v>1.364</v>
       </c>
       <c r="G2" t="n">
         <v>3.8714</v>
@@ -610,13 +610,13 @@
         <v>1.3648</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7717</v>
+        <v>1.2869</v>
       </c>
       <c r="T2" t="n">
         <v>0.6466</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1252</v>
+        <v>0.6403</v>
       </c>
       <c r="V2" t="n">
         <v>2.3386</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5807</v>
+        <v>3.5412</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1016</v>
+        <v>0.8681</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4792</v>
+        <v>2.6731</v>
       </c>
       <c r="G3" t="n">
         <v>2.8564</v>
@@ -688,13 +688,13 @@
         <v>1.8198</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6378</v>
+        <v>1.5982</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1375</v>
+        <v>0.904</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5003</v>
+        <v>0.6942</v>
       </c>
       <c r="V3" t="n">
         <v>2.9536</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7031</v>
+        <v>2.937</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6081</v>
+        <v>4.191</v>
       </c>
       <c r="F4" t="n">
-        <v>1.095</v>
+        <v>-1.254</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5276</v>
+        <v>2.7835</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.276</v>
+        <v>0.4861</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2516</v>
+        <v>2.2975</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3024</v>
+        <v>4.4267</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1534</v>
+        <v>1.4837</v>
       </c>
       <c r="L4" t="n">
-        <v>0.149</v>
+        <v>2.943</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.83</v>
+        <v>-1.6432</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4294</v>
+        <v>-0.9977</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4006</v>
+        <v>-0.6455</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4549</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5956</v>
+        <v>0.1526</v>
       </c>
       <c r="T4" t="n">
-        <v>1.353</v>
+        <v>-0.1884</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2426</v>
+        <v>0.341</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0901</v>
+        <v>0.2284</v>
       </c>
       <c r="W4" t="n">
         <v>1.0901</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8617</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2823</v>
+        <v>1.8468</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9225</v>
+        <v>1.0551</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6402</v>
+        <v>0.7917</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9893999999999999</v>
+        <v>0.0414</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.453</v>
+        <v>-0.2592</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5363</v>
+        <v>0.3006</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7857</v>
+        <v>-0.0799</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1152</v>
+        <v>-0.1916</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6705</v>
+        <v>0.1118</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7751</v>
+        <v>0.1213</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5682</v>
+        <v>-0.0675</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2069</v>
+        <v>0.1888</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4549</v>
+        <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6373</v>
+        <v>-0.1946</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9574</v>
+        <v>0.0449</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6798999999999999</v>
+        <v>-0.2395</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3167</v>
+        <v>1.0901</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3167</v>
+        <v>1.0901</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.829</v>
+        <v>1.8286</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3739</v>
+        <v>1.0245</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5449</v>
+        <v>0.8041</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7835</v>
+        <v>-0.5276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4861</v>
+        <v>-0.276</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2975</v>
+        <v>-0.2516</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4267</v>
+        <v>0.3024</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4837</v>
+        <v>0.1534</v>
       </c>
       <c r="L6" t="n">
-        <v>2.943</v>
+        <v>0.149</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6432</v>
+        <v>-0.83</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9977</v>
+        <v>-0.4294</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6455</v>
+        <v>-0.4006</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2275</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9099</v>
+        <v>0.6824</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9554</v>
+        <v>1.721</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0056</v>
+        <v>0.7693</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0501</v>
+        <v>0.9517</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2284</v>
+        <v>1.0901</v>
       </c>
       <c r="W6" t="n">
         <v>1.0901</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6654</v>
+        <v>1.1171</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9384</v>
+        <v>1.2581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.727</v>
+        <v>-0.141</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0414</v>
+        <v>1.2914</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2592</v>
+        <v>-0.953</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3006</v>
+        <v>2.2444</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0799</v>
+        <v>2.132</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1916</v>
+        <v>-0.8855</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1118</v>
+        <v>3.0175</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1213</v>
+        <v>-0.8406</v>
       </c>
       <c r="N7" t="n">
         <v>-0.0675</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1888</v>
+        <v>-0.7731</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9099</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>-1.1374</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9159</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.0901</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0.9099</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.376</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.0718</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.3042</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.0901</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.0901</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8118</v>
+        <v>-0.1119</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7911</v>
+        <v>-0.3104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0206</v>
+        <v>0.1985</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2914</v>
+        <v>1.4864</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.953</v>
+        <v>1.3986</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2444</v>
+        <v>0.0878</v>
       </c>
       <c r="J8" t="n">
-        <v>2.132</v>
+        <v>2.4552</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8855</v>
+        <v>1.9668</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0175</v>
+        <v>0.4884</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8406</v>
+        <v>-0.9688</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0675</v>
+        <v>-0.5682</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7731</v>
+        <v>-0.4006</v>
       </c>
       <c r="P8" t="n">
+        <v>-2.7297</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.4121</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.1314</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.1374</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1374</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6105</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.2035</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.0901</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4028</v>
+        <v>-0.1817</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3104</v>
+        <v>0.5878</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0924</v>
+        <v>-0.7695</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4864</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3986</v>
+        <v>-0.453</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0878</v>
+        <v>-0.5363</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4552</v>
+        <v>0.7857</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9668</v>
+        <v>0.1152</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4884</v>
+        <v>0.6705</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9688</v>
+        <v>-1.7751</v>
       </c>
       <c r="N9" t="n">
         <v>-0.5682</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4006</v>
+        <v>-1.2069</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7297</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4121</v>
+        <v>-1.1374</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6824</v>
+        <v>0.4549</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8405</v>
+        <v>1.1734</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6466</v>
+        <v>0.6227</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1939</v>
+        <v>0.5506</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3167</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3167</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5041</v>
+        <v>-1.1863</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9482</v>
+        <v>-0.598</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0.6851</v>
@@ -1234,13 +1234,13 @@
         <v>0.2275</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1892</v>
+        <v>0.1287</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5746</v>
+        <v>-0.2244</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3854</v>
+        <v>0.3531</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0901</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3641</v>
+        <v>-2.0407</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1202</v>
+        <v>-0.9777</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.244</v>
+        <v>-1.0631</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2468</v>
+        <v>-1.4573</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1714</v>
+        <v>-1.936</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0754</v>
+        <v>0.4787</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6892</v>
+        <v>0.264</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0518</v>
+        <v>-1.0771</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.741</v>
+        <v>1.3411</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5576</v>
+        <v>-1.7213</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2232</v>
+        <v>-0.8589</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3345</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2275</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2275</v>
+        <v>1.5923</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3448</v>
+        <v>0.2574</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.431</v>
+        <v>-0.2153</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0862</v>
+        <v>0.4727</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2485</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4068</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0069</v>
+        <v>-2.1181</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9115</v>
+        <v>-1.0034</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0954</v>
+        <v>-1.1147</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4573</v>
+        <v>-2.2468</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.936</v>
+        <v>-0.1714</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4787</v>
+        <v>-2.0754</v>
       </c>
       <c r="J12" t="n">
-        <v>0.264</v>
+        <v>-0.6892</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0771</v>
+        <v>0.0518</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3411</v>
+        <v>-0.741</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7213</v>
+        <v>-1.5576</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8589</v>
+        <v>-0.2232</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.3345</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5923</v>
+        <v>0.2275</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7089</v>
+        <v>-0.0987</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1492</v>
+        <v>-0.3142</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4404</v>
+        <v>0.2155</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2485</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5541</v>
+        <v>-7.1069</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4795</v>
+        <v>-5.1293</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0746</v>
+        <v>-1.9776</v>
       </c>
       <c r="G13" t="n">
         <v>-6.125</v>
@@ -1468,13 +1468,13 @@
         <v>0.2275</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6776</v>
+        <v>-0.2304</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7901</v>
+        <v>-0.4399</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1125</v>
+        <v>0.2094</v>
       </c>
       <c r="V13" t="n">
         <v>0.1583</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.249499999999998</v>
+        <v>6.249499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.326199999999998</v>
+        <v>7.326200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0768</v>
+        <v>-1.0767</v>
       </c>
       <c r="G14" t="n">
-        <v>1.669500000000001</v>
+        <v>1.669499999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-2.081300000000001</v>
@@ -1531,7 +1531,7 @@
         <v>-12.4189</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.3258</v>
+        <v>-5.325800000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-7.0932</v>
@@ -1546,13 +1546,13 @@
         <v>10.2363</v>
       </c>
       <c r="S14" t="n">
-        <v>7.841500000000002</v>
+        <v>7.841800000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>2.515299999999999</v>
+        <v>2.5154</v>
       </c>
       <c r="U14" t="n">
-        <v>5.3263</v>
+        <v>5.326199999999999</v>
       </c>
       <c r="V14" t="n">
         <v>5.837299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6969</v>
+        <v>4.7775</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5375</v>
+        <v>5.0705</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1595</v>
+        <v>-0.293</v>
       </c>
       <c r="G15" t="n">
         <v>2.9251</v>
@@ -1624,13 +1624,13 @@
         <v>2.9572</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0632</v>
+        <v>0.1437</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1674</v>
+        <v>-0.6343</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2305</v>
+        <v>0.778</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2485</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8023</v>
+        <v>1.6724</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2751</v>
+        <v>1.9249</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4728</v>
+        <v>-0.2525</v>
       </c>
       <c r="G16" t="n">
         <v>1.4626</v>
@@ -1702,13 +1702,13 @@
         <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8668</v>
+        <v>-0.9967</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1318</v>
+        <v>-0.2184</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9986</v>
+        <v>-0.7783</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1583</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2556</v>
+        <v>1.0796</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6442</v>
+        <v>2.1773</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3886</v>
+        <v>-1.0977</v>
       </c>
       <c r="G17" t="n">
         <v>2.1369</v>
@@ -1780,13 +1780,13 @@
         <v>2.9572</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.632</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4547</v>
+        <v>-0.9216</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1773</v>
+        <v>0.1136</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9318</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1086</v>
+        <v>0.6863</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2498</v>
+        <v>0.8335</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1412</v>
+        <v>-0.1471</v>
       </c>
       <c r="G18" t="n">
         <v>2.0347</v>
@@ -1858,13 +1858,13 @@
         <v>3.1846</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9515</v>
+        <v>-1.3738</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3647</v>
+        <v>-0.781</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5868</v>
+        <v>-0.5928</v>
       </c>
       <c r="V18" t="n">
         <v>-2.0219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7612</v>
+        <v>-0.5857</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3567</v>
+        <v>-1.2399</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5955</v>
+        <v>0.6542</v>
       </c>
       <c r="G19" t="n">
         <v>-0.314</v>
@@ -1936,13 +1936,13 @@
         <v>1.8198</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0823</v>
+        <v>-0.9069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6464</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4359</v>
+        <v>-0.3772</v>
       </c>
       <c r="V19" t="n">
         <v>1.0901</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.186</v>
+        <v>-1.089</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1648</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0212</v>
+        <v>-0.9242</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1189</v>
@@ -2014,13 +2014,13 @@
         <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.522</v>
+        <v>-0.425</v>
       </c>
       <c r="T20" t="n">
         <v>-0.431</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.091</v>
+        <v>0.006</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3712</v>
+        <v>-2.0072</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2027</v>
+        <v>-2.7358</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8315</v>
+        <v>0.7286</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1362</v>
@@ -2092,13 +2092,13 @@
         <v>2.5022</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4416</v>
+        <v>-1.0775</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1492</v>
+        <v>-0.6823</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2923</v>
+        <v>-0.3953</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1583</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6793</v>
+        <v>-3.207</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.297</v>
+        <v>-1.1803</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3823</v>
+        <v>-2.0268</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4071</v>
@@ -2170,13 +2170,13 @@
         <v>1.5923</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8164</v>
+        <v>-0.3441</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5865</v>
+        <v>-0.4697</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2299</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7734</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1152</v>
+        <v>-6.7979</v>
       </c>
       <c r="E23" t="n">
         <v>-3.6086</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5066</v>
+        <v>-3.1893</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2526</v>
@@ -2248,13 +2248,13 @@
         <v>2.5022</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5922</v>
+        <v>-1.275</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6583</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.6167</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6352</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.249499999999999</v>
+        <v>-5.471</v>
       </c>
       <c r="E24" t="n">
         <v>1.0768</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.3262</v>
+        <v>-6.5478</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6695</v>
@@ -2326,13 +2326,13 @@
         <v>19.3352</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.841600000000001</v>
+        <v>-7.0633</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.3264</v>
+        <v>-5.3263</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5153</v>
+        <v>-1.7371</v>
       </c>
       <c r="V24" t="n">
         <v>-5.8373</v>
